--- a/display/PackConfig_v2.xlsx
+++ b/display/PackConfig_v2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="PackConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PackConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -912,6 +912,8 @@
       </c>
       <c r="B34" s="3" t="n"/>
       <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -926,6 +928,16 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>GuaranteedMinRarity</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>GuaranteedNewSnap</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -939,7 +951,13 @@
       <c r="B36" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="6" t="inlineStr"/>
+      <c r="C36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -950,7 +968,13 @@
       <c r="B37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C37" s="6" t="inlineStr"/>
+      <c r="C37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -961,7 +985,13 @@
       <c r="B38" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="6" t="inlineStr"/>
+      <c r="C38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -972,7 +1002,13 @@
       <c r="B39" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C39" s="6" t="inlineStr"/>
+      <c r="C39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -983,7 +1019,13 @@
       <c r="B40" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="6" t="inlineStr"/>
+      <c r="C40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -994,127 +1036,97 @@
       <c r="B41" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C41" s="6" t="inlineStr"/>
+      <c r="C41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Cards/Open and the pity table below are the ONLY things that differentiate pack tiers (D19/9) — the rarity odds are identical for all of them and come from the SNAP POOL.</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>GuaranteedMinRarity: the pack contains at least one card of AT LEAST this rarity, given as the 1-based ROW NUMBER in RARITY DEFINITIONS above (1 = the first row, 6 = the last). 0 = no guarantee.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
+          <t>GuaranteedNewSnap: the pack contains at least this many cards the player does not already own. 0 = no guarantee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Both are FLOORS ON THE FINISHED PACK, not extra cards: they never change how many cards a pack gives (that stays Cards/Open), and a card drawn naturally counts towards them. One card that is both new and above the floor satisfies both at once. Where the pool cannot meet a floor — no unowned card left, or no copies at that rarity — the draw degrades to the best available rather than failing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>GuaranteedNewSnap also stands in for the engine's built-in dry-streak pity on any pack where it is set: the two make the same promise, so only one of them runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Cards/Open and the pity table below are the ONLY things that differentiate pack tiers (D19/9) — the rarity odds are identical for all of them and come from the SNAP POOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
           <t>The old PACK RARITY PROBABILITIES grid was removed 2026-08-03: it multiplied the pool counts, applying rarity twice.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>PACK PITY CONFIG</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="B49" s="3" t="n"/>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Pack Type</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>PityProbabilities</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>PityForceHighestRarity</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>1-star Pack</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>2-star Pack</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="6" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>3-star Pack</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="6" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>4-star Pack</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>5-star Pack</t>
+          <t>1-star Pack</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>[0, 0.33, 0.66, 1.0]</t>
+          <t>[0]</t>
         </is>
       </c>
       <c r="C51" s="6" t="b">
@@ -1125,647 +1137,431 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>2-star Pack</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>3-star Pack</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>4-star Pack</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>[0, 0.33, 0.66, 1.0]</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
           <t>6-star Pack</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>[0, 0.8, 0.8, 1.0]</t>
         </is>
       </c>
-      <c r="C52" s="6" t="b">
+      <c r="C56" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="D52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>SEMANTICS (implemented 2026-08-03; this table existed but was never read):</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>PityProbabilities is indexed by the number of CONSECUTIVE MISSES of the target rarity — NOT by card slot. p[0] applies to a pull with no misses behind it, p[1] after one miss, p[2] after two, and so on; entries past the end reuse the LAST value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>So [0, 0.8, 0.8, 1.0] reads: no help at first; miss once and the next pull has an 80% chance of the target rarity; miss again, another 80%; miss a third time and the next pull is GUARANTEED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>The counter RESETS to 0 the moment a pull lands on the target rarity — whether pity forced it or the player got there naturally — and starts at 0 on every pack open. It does NOT carry between packs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Target rarity = the highest rarity that STILL HAS COPIES in the snap pool when PityForceHighestRarity is TRUE. That is also the empty-tier fallback: Gold ships at Qty 0, so a 6-star pack's pity resolves to 5★ until Gold has stock, instead of chasing a card that cannot be drawn. When FALSE, the target is any rarity above the pool's most-stocked one.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
+          <t>PityProbabilities is indexed by the number of CONSECUTIVE MISSES of the target rarity — NOT by card slot. p[0] applies to a pull with no misses behind it, p[1] after one miss, p[2] after two, and so on; entries past the end reuse the LAST value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>So [0, 0.8, 0.8, 1.0] reads: no help at first; miss once and the next pull has an 80% chance of the target rarity; miss again, another 80%; miss a third time and the next pull is GUARANTEED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>The counter RESETS to 0 the moment a pull lands on the target rarity — whether pity forced it or the player got there naturally — and starts at 0 on every pack open. It does NOT carry between packs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Target rarity = the highest rarity that STILL HAS COPIES in the snap pool when PityForceHighestRarity is TRUE. That is also the empty-tier fallback: Gold ships at Qty 0, so a 6-star pack's pity resolves to 5★ until Gold has stock, instead of chasing a card that cannot be drawn. When FALSE, the target is any rarity above the pool's most-stocked one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
           <t>This is SEPARATE from the dry-streak pity in CardOpenings.gs, which chases a NEW card rather than a rare one (after 3 consecutive packs with no new card, the last card is forced to be an unowned type).</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>STAR CHEST COSTS &amp; REWARDS</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="B64" s="3" t="n"/>
+      <c r="C64" s="3" t="n"/>
+      <c r="D64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Chest Tier</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Cost (Stars)</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Reward Pack Type</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B66" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>1-star Pack</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B67" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>4-star Pack</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>5-star Pack</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CHEST PURCHASING</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="D67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>5-star Pack</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>CHEST PURCHASING</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t>Min Stars to Consider Buying</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B72" s="6" t="n">
         <v>250</v>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>no purchase below this star balance</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Urgency Start Day</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B73" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>before this day the buy probability is 0%</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>End-of-Season Buy Probability</t>
         </is>
       </c>
-      <c r="B70" s="6" t="n">
+      <c r="B74" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>buy probability on the final day; ramps linearly from 0% at Urgency Start Day</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>Migrated from the deleted PlayerBehavior sheet 2026-08-03 and now actually READ: the sim used to ignore all three and buy greedily after 85% of the season.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>SET REWARDS</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
-      <c r="P73" s="3" t="n"/>
-      <c r="Q73" s="3" t="n"/>
-      <c r="R73" s="3" t="n"/>
-      <c r="S73" s="3" t="n"/>
-      <c r="T73" s="3" t="n"/>
-      <c r="U73" s="3" t="n"/>
-      <c r="V73" s="3" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
+      <c r="M77" s="3" t="n"/>
+      <c r="N77" s="3" t="n"/>
+      <c r="O77" s="3" t="n"/>
+      <c r="P77" s="3" t="n"/>
+      <c r="Q77" s="3" t="n"/>
+      <c r="R77" s="3" t="n"/>
+      <c r="S77" s="3" t="n"/>
+      <c r="T77" s="3" t="n"/>
+      <c r="U77" s="3" t="n"/>
+      <c r="V77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Set ID</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Coins</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>SPT</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>SPT x2</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>Chuck</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>Bomb</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>Slingshot</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>Shuffle</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>Unlimited Lives</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>Unlimited Red</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>Unlimited Chuck</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>Unlimited Bomb</t>
         </is>
       </c>
-      <c r="O74" s="4" t="inlineStr">
+      <c r="O78" s="4" t="inlineStr">
         <is>
           <t>COOP Token</t>
         </is>
       </c>
-      <c r="P74" s="4" t="inlineStr">
+      <c r="P78" s="4" t="inlineStr">
         <is>
           <t>Avatar</t>
         </is>
       </c>
-      <c r="Q74" s="4" t="inlineStr">
+      <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>1-star Dly</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr">
+      <c r="R78" s="4" t="inlineStr">
         <is>
           <t>2-star Dly</t>
         </is>
       </c>
-      <c r="S74" s="4" t="inlineStr">
+      <c r="S78" s="4" t="inlineStr">
         <is>
           <t>3-star Dly</t>
         </is>
       </c>
-      <c r="T74" s="4" t="inlineStr">
+      <c r="T78" s="4" t="inlineStr">
         <is>
           <t>4-star Dly</t>
         </is>
       </c>
-      <c r="U74" s="4" t="inlineStr">
+      <c r="U78" s="4" t="inlineStr">
         <is>
           <t>5-star Dly</t>
         </is>
       </c>
-      <c r="V74" s="4" t="inlineStr">
+      <c r="V78" s="4" t="inlineStr">
         <is>
           <t>6-star Dly</t>
         </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Set 1</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="L75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Set 2</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>Set 3</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Set 4</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Set 5</t>
+          <t>Set 1</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C79" s="6" t="n">
         <v>0</v>
@@ -1774,10 +1570,10 @@
         <v>0</v>
       </c>
       <c r="E79" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="6" t="n">
         <v>0</v>
@@ -1792,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>0</v>
@@ -1831,11 +1627,11 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Set 6</t>
+          <t>Set 2</t>
         </is>
       </c>
       <c r="B80" s="6" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C80" s="6" t="n">
         <v>0</v>
@@ -1847,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6" t="n">
         <v>0</v>
@@ -1901,11 +1697,11 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Set 7</t>
+          <t>Set 3</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C81" s="6" t="n">
         <v>0</v>
@@ -1920,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I81" s="6" t="n">
         <v>0</v>
@@ -1971,7 +1767,7 @@
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Set 8</t>
+          <t>Set 4</t>
         </is>
       </c>
       <c r="B82" s="6" t="n">
@@ -1984,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>0</v>
@@ -1996,407 +1792,687 @@
         <v>0</v>
       </c>
       <c r="I82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Set 5</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="6" t="n">
+      <c r="G83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>ALBUM REWARDS</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="3" t="n"/>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
-      <c r="P84" s="3" t="n"/>
-      <c r="Q84" s="3" t="n"/>
-      <c r="R84" s="3" t="n"/>
-      <c r="S84" s="3" t="n"/>
-      <c r="T84" s="3" t="n"/>
-      <c r="U84" s="3" t="n"/>
-      <c r="V84" s="3" t="n"/>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Set 6</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
-        <is>
-          <t>Album ID</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Coins</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>SPT</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>SPT x2</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Chuck</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Bomb</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Slingshot</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>Shuffle</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>Comet</t>
-        </is>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Lives</t>
-        </is>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Red</t>
-        </is>
-      </c>
-      <c r="M85" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Chuck</t>
-        </is>
-      </c>
-      <c r="N85" s="4" t="inlineStr">
-        <is>
-          <t>Unlimited Bomb</t>
-        </is>
-      </c>
-      <c r="O85" s="4" t="inlineStr">
-        <is>
-          <t>COOP Token</t>
-        </is>
-      </c>
-      <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>Avatar</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>1-star Dly</t>
-        </is>
-      </c>
-      <c r="R85" s="4" t="inlineStr">
-        <is>
-          <t>2-star Dly</t>
-        </is>
-      </c>
-      <c r="S85" s="4" t="inlineStr">
-        <is>
-          <t>3-star Dly</t>
-        </is>
-      </c>
-      <c r="T85" s="4" t="inlineStr">
-        <is>
-          <t>4-star Dly</t>
-        </is>
-      </c>
-      <c r="U85" s="4" t="inlineStr">
-        <is>
-          <t>5-star Dly</t>
-        </is>
-      </c>
-      <c r="V85" s="4" t="inlineStr">
-        <is>
-          <t>6-star Dly</t>
-        </is>
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Set 7</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>Set 8</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>ALBUM REWARDS</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
+      <c r="J88" s="3" t="n"/>
+      <c r="K88" s="3" t="n"/>
+      <c r="L88" s="3" t="n"/>
+      <c r="M88" s="3" t="n"/>
+      <c r="N88" s="3" t="n"/>
+      <c r="O88" s="3" t="n"/>
+      <c r="P88" s="3" t="n"/>
+      <c r="Q88" s="3" t="n"/>
+      <c r="R88" s="3" t="n"/>
+      <c r="S88" s="3" t="n"/>
+      <c r="T88" s="3" t="n"/>
+      <c r="U88" s="3" t="n"/>
+      <c r="V88" s="3" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Album ID</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Coins</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>SPT</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>SPT x2</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Chuck</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>Bomb</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Slingshot</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>Shuffle</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Comet</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Lives</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Red</t>
+        </is>
+      </c>
+      <c r="M89" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Chuck</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>Unlimited Bomb</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>COOP Token</t>
+        </is>
+      </c>
+      <c r="P89" s="4" t="inlineStr">
+        <is>
+          <t>Avatar</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>1-star Dly</t>
+        </is>
+      </c>
+      <c r="R89" s="4" t="inlineStr">
+        <is>
+          <t>2-star Dly</t>
+        </is>
+      </c>
+      <c r="S89" s="4" t="inlineStr">
+        <is>
+          <t>3-star Dly</t>
+        </is>
+      </c>
+      <c r="T89" s="4" t="inlineStr">
+        <is>
+          <t>4-star Dly</t>
+        </is>
+      </c>
+      <c r="U89" s="4" t="inlineStr">
+        <is>
+          <t>5-star Dly</t>
+        </is>
+      </c>
+      <c r="V89" s="4" t="inlineStr">
+        <is>
+          <t>6-star Dly</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
           <t>Album 1</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B90" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="C86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="6" t="n">
+      <c r="C90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="F90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Album 2</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="6" t="n">
+      <c r="B91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="6" t="n">
+      <c r="D91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="G91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>Album 3</t>
         </is>
       </c>
-      <c r="B88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="6" t="n">
+      <c r="B92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="H92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>An album index beyond the last row defined here reuses that last row (albums loop).</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>Set / Album reward payouts land in the SimOutput pack-log Note column. They are NOT fed back into EcoGainsSim — the card sim is a downstream consumer of the pack flow, not a source in the 25-category universe.</t>
         </is>
